--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4554" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4554" uniqueCount="616">
   <si>
     <t>Property</t>
   </si>
@@ -632,7 +632,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -919,6 +919,14 @@
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="LP89803-8"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Observation.category:second.id</t>
   </si>
   <si>
@@ -935,9 +943,6 @@
   </si>
   <si>
     <t>Observation.category:second.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.category:second.coding.version</t>
@@ -1071,6 +1076,9 @@
   </si>
   <si>
     <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.code.coding.version</t>
@@ -4824,7 +4832,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -5589,7 +5597,7 @@
         <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>83</v>
@@ -5663,7 +5671,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>207</v>
@@ -5781,7 +5789,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>214</v>
@@ -5901,7 +5909,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>220</v>
@@ -6023,7 +6031,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>230</v>
@@ -6141,7 +6149,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>232</v>
@@ -6261,7 +6269,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>234</v>
@@ -6272,7 +6280,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>94</v>
@@ -6306,7 +6314,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>297</v>
+        <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -7718,7 +7726,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>94</v>
@@ -9198,7 +9206,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>297</v>
+        <v>342</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9275,10 +9283,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9395,10 +9403,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9438,7 +9446,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9515,10 +9523,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9561,7 +9569,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9635,10 +9643,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9757,10 +9765,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9879,10 +9887,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9905,19 +9913,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9966,7 +9974,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9981,19 +9989,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -10001,10 +10009,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10027,16 +10035,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10086,7 +10094,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10110,10 +10118,10 @@
         <v>331</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10121,14 +10129,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10147,19 +10155,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10208,7 +10216,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10223,19 +10231,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10243,14 +10251,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10269,19 +10277,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10330,7 +10338,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10345,19 +10353,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10365,10 +10373,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10391,16 +10399,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10450,7 +10458,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10471,13 +10479,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10485,10 +10493,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10511,19 +10519,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10572,7 +10580,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10587,19 +10595,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10607,10 +10615,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10636,16 +10644,16 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10674,7 +10682,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -10692,7 +10700,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10701,7 +10709,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10710,27 +10718,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10756,16 +10764,16 @@
         <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10790,13 +10798,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10814,7 +10822,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10823,7 +10831,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10838,7 +10846,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10849,14 +10857,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10878,16 +10886,16 @@
         <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10912,13 +10920,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10936,7 +10944,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10954,27 +10962,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10997,19 +11005,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11058,7 +11066,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11079,10 +11087,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11093,10 +11101,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11122,13 +11130,13 @@
         <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11158,7 +11166,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11176,7 +11184,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11194,27 +11202,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11329,10 +11337,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11449,13 +11457,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="B77" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="C77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
@@ -11477,13 +11485,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11569,10 +11577,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11687,10 +11695,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11716,10 +11724,10 @@
         <v>140</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11805,10 +11813,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11834,13 +11842,13 @@
         <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11848,7 +11856,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>83</v>
@@ -11890,7 +11898,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>94</v>
@@ -11925,10 +11933,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11954,10 +11962,10 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11988,7 +11996,7 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12006,7 +12014,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12041,10 +12049,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12159,10 +12167,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12279,10 +12287,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12401,10 +12409,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12519,10 +12527,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12639,10 +12647,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12684,7 +12692,7 @@
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>83</v>
@@ -12761,10 +12769,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12881,10 +12889,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13001,10 +13009,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13121,10 +13129,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13243,10 +13251,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13365,10 +13373,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13487,10 +13495,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13609,10 +13617,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13638,16 +13646,16 @@
         <v>191</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13675,10 +13683,10 @@
         <v>326</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -13696,7 +13704,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13717,10 +13725,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13731,10 +13739,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13757,16 +13765,16 @@
         <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13816,7 +13824,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13834,27 +13842,27 @@
         <v>83</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13877,16 +13885,16 @@
         <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13936,7 +13944,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13954,27 +13962,27 @@
         <v>83</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13997,19 +14005,19 @@
         <v>83</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -14058,7 +14066,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14070,7 +14078,7 @@
         <v>83</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>83</v>
@@ -14079,10 +14087,10 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14093,10 +14101,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14211,10 +14219,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14331,14 +14339,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14360,10 +14368,10 @@
         <v>140</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>143</v>
@@ -14418,7 +14426,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14453,10 +14461,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14479,13 +14487,13 @@
         <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14536,7 +14544,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14545,7 +14553,7 @@
         <v>94</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>106</v>
@@ -14557,10 +14565,10 @@
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14571,10 +14579,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14597,13 +14605,13 @@
         <v>83</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14654,7 +14662,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14663,7 +14671,7 @@
         <v>94</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>106</v>
@@ -14675,10 +14683,10 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14689,10 +14697,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14718,16 +14726,16 @@
         <v>191</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -14755,10 +14763,10 @@
         <v>118</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>83</v>
@@ -14776,7 +14784,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14794,13 +14802,13 @@
         <v>83</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14811,10 +14819,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14840,16 +14848,16 @@
         <v>191</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -14877,10 +14885,10 @@
         <v>326</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -14898,7 +14906,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14916,13 +14924,13 @@
         <v>83</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -14933,10 +14941,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14959,17 +14967,17 @@
         <v>83</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -15018,7 +15026,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15042,7 +15050,7 @@
         <v>83</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15053,10 +15061,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15082,10 +15090,10 @@
         <v>208</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15136,7 +15144,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15157,10 +15165,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15171,10 +15179,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15197,16 +15205,16 @@
         <v>95</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15256,7 +15264,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15277,10 +15285,10 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15291,10 +15299,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15317,16 +15325,16 @@
         <v>95</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15376,7 +15384,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15397,10 +15405,10 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -15411,10 +15419,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15437,19 +15445,19 @@
         <v>95</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -15498,7 +15506,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15519,10 +15527,10 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>83</v>
@@ -15533,10 +15541,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15651,10 +15659,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15771,14 +15779,14 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -15800,10 +15808,10 @@
         <v>140</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>143</v>
@@ -15858,7 +15866,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15893,10 +15901,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15922,13 +15930,13 @@
         <v>191</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O114" t="s" s="2">
         <v>325</v>
@@ -15980,7 +15988,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>94</v>
@@ -15998,7 +16006,7 @@
         <v>83</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>331</v>
@@ -16015,10 +16023,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16041,19 +16049,19 @@
         <v>95</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
@@ -16102,7 +16110,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16120,27 +16128,27 @@
         <v>83</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16166,16 +16174,16 @@
         <v>191</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -16200,13 +16208,13 @@
         <v>83</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>83</v>
@@ -16224,7 +16232,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16233,7 +16241,7 @@
         <v>94</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>106</v>
@@ -16248,7 +16256,7 @@
         <v>137</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>83</v>
@@ -16259,14 +16267,14 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -16288,16 +16296,16 @@
         <v>191</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -16322,13 +16330,13 @@
         <v>83</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>83</v>
@@ -16346,7 +16354,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -16364,27 +16372,27 @@
         <v>83</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16410,16 +16418,16 @@
         <v>84</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -16468,7 +16476,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16489,10 +16497,10 @@
         <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4554" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4554" uniqueCount="614">
   <si>
     <t>Property</t>
   </si>
@@ -657,6 +657,14 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="exam"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -811,9 +819,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>exam</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -951,9 +956,6 @@
     <t>Observation.category:second.coding.code</t>
   </si>
   <si>
-    <t>LP89803-8</t>
-  </si>
-  <si>
     <t>Observation.category:second.coding.display</t>
   </si>
   <si>
@@ -972,6 +974,14 @@
     <t>このObservationに関する詳細分類、JP_ObservationDetailedDentalCategory_VSより選択する、必須項目</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS"/&gt;
+    &lt;code value="DO-1-01"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDetailedDentalCategory_VS</t>
   </si>
   <si>
@@ -993,16 +1003,10 @@
     <t>Observation.category:third.coding.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS</t>
-  </si>
-  <si>
     <t>Observation.category:third.coding.version</t>
   </si>
   <si>
     <t>Observation.category:third.coding.code</t>
-  </si>
-  <si>
-    <t>DO-1-01</t>
   </si>
   <si>
     <t>Observation.category:third.coding.display</t>
@@ -1112,7 +1116,7 @@
     <t>観察対象者 【JP Core仕様】患者情報</t>
   </si>
   <si>
-    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明なデバイスによって観察が行われるケースである。この場合、観察は何らかのコンテキスト/チャネルマッチング技術を介して患者にマッチングされる必要があり、患者にマッチングされれば、その時点で本要素を更新する必要がある。</t>
+    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明な機器によって観察が行われるケースである。この場合、観察は何らかのコンテキスト・チャネル照合技術を介して患者に照合される必要があり、患者に照合されれば、その時点で本要素を更新する必要がある。</t>
   </si>
   <si>
     <t>あなたが彼らが誰または何をしているのかわからない場合、観察には価値がありません。 / Observations have no value if you don't know who or what they're about.</t>
@@ -1157,7 +1161,7 @@
 </t>
   </si>
   <si>
-    <t>このobservationが行われるヘルスケアイベント</t>
+    <t>このobservationが行われる診療イベント</t>
   </si>
   <si>
     <t>例：診療、歯科検診、身元不明者調査</t>
@@ -4151,7 +4155,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -4170,7 +4174,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4223,10 +4227,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4249,13 +4253,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4306,7 +4310,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4330,7 +4334,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4341,10 +4345,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4373,7 +4377,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4414,10 +4418,10 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
@@ -4426,7 +4430,7 @@
         <v>198</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4450,7 +4454,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4461,10 +4465,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4487,19 +4491,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4548,7 +4552,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4569,10 +4573,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4583,10 +4587,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4609,13 +4613,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4666,7 +4670,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4690,7 +4694,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4701,10 +4705,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4733,7 +4737,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4774,10 +4778,10 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
@@ -4786,7 +4790,7 @@
         <v>198</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4810,7 +4814,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4821,10 +4825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4850,23 +4854,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4908,7 +4912,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4929,10 +4933,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4943,10 +4947,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4969,16 +4973,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5028,7 +5032,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5049,10 +5053,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5063,10 +5067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5092,21 +5096,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>256</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -5209,7 +5213,7 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>262</v>
@@ -5451,7 +5455,7 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>280</v>
@@ -5674,7 +5678,7 @@
         <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5697,13 +5701,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5754,7 +5758,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5778,7 +5782,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5792,7 +5796,7 @@
         <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5821,7 +5825,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5862,10 +5866,10 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
@@ -5874,7 +5878,7 @@
         <v>198</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5898,7 +5902,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5912,7 +5916,7 @@
         <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5935,19 +5939,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5996,7 +6000,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6017,10 +6021,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -6034,7 +6038,7 @@
         <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6057,13 +6061,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6114,7 +6118,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6138,7 +6142,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6152,7 +6156,7 @@
         <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6181,7 +6185,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -6222,10 +6226,10 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
@@ -6234,7 +6238,7 @@
         <v>198</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6258,7 +6262,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6272,7 +6276,7 @@
         <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6298,16 +6302,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6356,7 +6360,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6377,10 +6381,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6394,7 +6398,7 @@
         <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6417,16 +6421,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6476,7 +6480,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6497,10 +6501,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6514,7 +6518,7 @@
         <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6540,21 +6544,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6631,7 +6635,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>261</v>
@@ -6657,7 +6661,7 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>262</v>
@@ -6751,7 +6755,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>269</v>
@@ -6873,7 +6877,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>279</v>
@@ -6899,7 +6903,7 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>280</v>
@@ -6995,13 +6999,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>189</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -7026,10 +7030,10 @@
         <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>290</v>
@@ -7045,7 +7049,7 @@
         <v>83</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>83</v>
@@ -7120,7 +7124,7 @@
         <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7143,13 +7147,13 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7200,7 +7204,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7224,7 +7228,7 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7238,7 +7242,7 @@
         <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7267,7 +7271,7 @@
         <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>143</v>
@@ -7308,10 +7312,10 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>83</v>
@@ -7320,7 +7324,7 @@
         <v>198</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7344,7 +7348,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7358,7 +7362,7 @@
         <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7381,19 +7385,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7442,7 +7446,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7463,10 +7467,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7480,7 +7484,7 @@
         <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7503,13 +7507,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7560,7 +7564,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7584,7 +7588,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7598,7 +7602,7 @@
         <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7627,7 +7631,7 @@
         <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -7668,10 +7672,10 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
@@ -7680,7 +7684,7 @@
         <v>198</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7704,7 +7708,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7718,7 +7722,7 @@
         <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7744,23 +7748,23 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7802,7 +7806,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7823,10 +7827,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7837,10 +7841,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7863,16 +7867,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7922,7 +7926,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7943,10 +7947,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7957,10 +7961,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7986,21 +7990,21 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -8077,7 +8081,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>261</v>
@@ -8103,7 +8107,7 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>262</v>
@@ -8197,7 +8201,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>269</v>
@@ -8319,7 +8323,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>279</v>
@@ -8345,7 +8349,7 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>280</v>
@@ -8441,14 +8445,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8470,16 +8474,16 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8504,14 +8508,14 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8528,7 +8532,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8543,30 +8547,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8589,13 +8593,13 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8646,7 +8650,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8670,7 +8674,7 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8681,10 +8685,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8713,7 +8717,7 @@
         <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8754,10 +8758,10 @@
         <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>83</v>
@@ -8766,7 +8770,7 @@
         <v>198</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8790,7 +8794,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8801,10 +8805,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8827,19 +8831,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8888,7 +8892,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8909,10 +8913,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8923,10 +8927,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8949,13 +8953,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9006,7 +9010,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9030,7 +9034,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -9041,10 +9045,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9073,7 +9077,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -9114,10 +9118,10 @@
         <v>83</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>83</v>
@@ -9126,7 +9130,7 @@
         <v>198</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9150,7 +9154,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9161,10 +9165,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9190,23 +9194,23 @@
         <v>108</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9248,7 +9252,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9269,10 +9273,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9283,10 +9287,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9309,16 +9313,16 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9368,7 +9372,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9389,10 +9393,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9403,10 +9407,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9432,21 +9436,21 @@
         <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9523,10 +9527,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9549,7 +9553,7 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>262</v>
@@ -9569,7 +9573,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9643,10 +9647,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9765,10 +9769,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9791,7 +9795,7 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>280</v>
@@ -9887,10 +9891,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9913,19 +9917,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9974,7 +9978,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9989,19 +9993,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AL64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -10009,10 +10013,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10035,16 +10039,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10094,7 +10098,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10115,13 +10119,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10129,14 +10133,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10155,19 +10159,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10216,7 +10220,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10231,19 +10235,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AL66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10251,14 +10255,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10277,19 +10281,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10338,7 +10342,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10353,19 +10357,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10373,10 +10377,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10399,16 +10403,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10458,7 +10462,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10479,13 +10483,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10493,10 +10497,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10519,19 +10523,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10580,7 +10584,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10595,19 +10599,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AL69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10615,10 +10619,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10644,16 +10648,16 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O70" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10682,7 +10686,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -10700,7 +10704,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10709,7 +10713,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10718,27 +10722,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>409</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10764,16 +10768,16 @@
         <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="O71" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10798,14 +10802,14 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="Y71" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10822,7 +10826,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10831,7 +10835,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10846,7 +10850,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10857,14 +10861,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10886,16 +10890,16 @@
         <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O72" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10920,13 +10924,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10944,7 +10948,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10962,27 +10966,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>429</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11005,19 +11009,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11066,7 +11070,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11087,10 +11091,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11101,10 +11105,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11130,13 +11134,13 @@
         <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11166,7 +11170,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11184,7 +11188,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11202,27 +11206,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>444</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11245,13 +11249,13 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11302,7 +11306,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11326,7 +11330,7 @@
         <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11337,10 +11341,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11369,7 +11373,7 @@
         <v>141</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>143</v>
@@ -11410,10 +11414,10 @@
         <v>83</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>83</v>
@@ -11422,7 +11426,7 @@
         <v>198</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11446,7 +11450,7 @@
         <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11457,13 +11461,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B77" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
@@ -11485,13 +11489,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11542,7 +11546,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11577,10 +11581,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11603,13 +11607,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11660,7 +11664,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11684,7 +11688,7 @@
         <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11695,10 +11699,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11724,10 +11728,10 @@
         <v>140</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11766,10 +11770,10 @@
         <v>83</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>83</v>
@@ -11778,7 +11782,7 @@
         <v>198</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11813,10 +11817,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11842,13 +11846,13 @@
         <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11856,7 +11860,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>83</v>
@@ -11898,7 +11902,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>94</v>
@@ -11933,10 +11937,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11962,10 +11966,10 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11996,7 +12000,7 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12014,7 +12018,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12049,10 +12053,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12075,13 +12079,13 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12132,7 +12136,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12156,7 +12160,7 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12167,10 +12171,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12199,7 +12203,7 @@
         <v>141</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>143</v>
@@ -12240,10 +12244,10 @@
         <v>83</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>83</v>
@@ -12252,7 +12256,7 @@
         <v>198</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12276,7 +12280,7 @@
         <v>83</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12287,10 +12291,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12313,19 +12317,19 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12374,7 +12378,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12395,10 +12399,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12409,10 +12413,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12435,13 +12439,13 @@
         <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12492,7 +12496,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12516,7 +12520,7 @@
         <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12527,10 +12531,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12559,7 +12563,7 @@
         <v>141</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>143</v>
@@ -12600,10 +12604,10 @@
         <v>83</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>83</v>
@@ -12612,7 +12616,7 @@
         <v>198</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12636,7 +12640,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12647,10 +12651,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12676,23 +12680,23 @@
         <v>108</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>83</v>
@@ -12734,7 +12738,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12755,10 +12759,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12769,10 +12773,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12795,16 +12799,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12854,7 +12858,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12875,10 +12879,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12889,10 +12893,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12918,14 +12922,14 @@
         <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -13009,10 +13013,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13035,7 +13039,7 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>262</v>
@@ -13129,10 +13133,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13251,10 +13255,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13277,7 +13281,7 @@
         <v>95</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>280</v>
@@ -13373,10 +13377,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13399,19 +13403,19 @@
         <v>95</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13460,7 +13464,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13481,10 +13485,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13495,10 +13499,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13521,7 +13525,7 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>280</v>
@@ -13617,10 +13621,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13646,16 +13650,16 @@
         <v>191</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="O95" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13680,13 +13684,13 @@
         <v>83</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -13704,7 +13708,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13725,10 +13729,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13739,10 +13743,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13765,16 +13769,16 @@
         <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13824,7 +13828,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13842,27 +13846,27 @@
         <v>83</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="AM96" t="s" s="2">
+      <c r="AO96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP96" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>510</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13885,16 +13889,16 @@
         <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13944,7 +13948,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13962,27 +13966,27 @@
         <v>83</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="AM97" t="s" s="2">
+      <c r="AO97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP97" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>518</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14005,19 +14009,19 @@
         <v>83</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N98" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -14066,7 +14070,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14078,19 +14082,19 @@
         <v>83</v>
       </c>
       <c r="AJ98" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14101,10 +14105,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14127,13 +14131,13 @@
         <v>83</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14184,7 +14188,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14208,7 +14212,7 @@
         <v>83</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14219,10 +14223,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14251,7 +14255,7 @@
         <v>141</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>143</v>
@@ -14304,7 +14308,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14328,7 +14332,7 @@
         <v>83</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
@@ -14339,14 +14343,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14368,10 +14372,10 @@
         <v>140</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>143</v>
@@ -14426,7 +14430,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14461,10 +14465,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14487,13 +14491,13 @@
         <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14544,7 +14548,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14553,7 +14557,7 @@
         <v>94</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>106</v>
@@ -14565,10 +14569,10 @@
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14579,10 +14583,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14605,13 +14609,13 @@
         <v>83</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14662,7 +14666,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14671,7 +14675,7 @@
         <v>94</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>106</v>
@@ -14683,10 +14687,10 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14697,10 +14701,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14726,16 +14730,16 @@
         <v>191</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -14763,10 +14767,10 @@
         <v>118</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>83</v>
@@ -14784,7 +14788,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14802,13 +14806,13 @@
         <v>83</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14819,10 +14823,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14848,16 +14852,16 @@
         <v>191</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -14882,13 +14886,13 @@
         <v>83</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -14906,7 +14910,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14924,13 +14928,13 @@
         <v>83</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -14941,10 +14945,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14967,17 +14971,17 @@
         <v>83</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -15026,7 +15030,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15050,7 +15054,7 @@
         <v>83</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15061,10 +15065,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15087,13 +15091,13 @@
         <v>83</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15144,7 +15148,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15165,10 +15169,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15179,10 +15183,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15205,16 +15209,16 @@
         <v>95</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15264,7 +15268,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15285,10 +15289,10 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15299,10 +15303,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15325,16 +15329,16 @@
         <v>95</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N109" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15384,7 +15388,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15405,10 +15409,10 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -15419,10 +15423,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15445,19 +15449,19 @@
         <v>95</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="O110" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -15506,7 +15510,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15527,10 +15531,10 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>83</v>
@@ -15541,10 +15545,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15567,13 +15571,13 @@
         <v>83</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15624,7 +15628,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -15648,7 +15652,7 @@
         <v>83</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>83</v>
@@ -15659,10 +15663,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15691,7 +15695,7 @@
         <v>141</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>143</v>
@@ -15744,7 +15748,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15768,7 +15772,7 @@
         <v>83</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
@@ -15779,14 +15783,14 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -15808,10 +15812,10 @@
         <v>140</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>143</v>
@@ -15866,7 +15870,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15901,10 +15905,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15930,16 +15934,16 @@
         <v>191</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N114" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="M114" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>594</v>
-      </c>
       <c r="O114" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -15964,14 +15968,14 @@
         <v>83</v>
       </c>
       <c r="X114" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z114" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Y114" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
       </c>
@@ -15988,7 +15992,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>94</v>
@@ -16006,16 +16010,16 @@
         <v>83</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AM114" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AO114" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>83</v>
@@ -16023,10 +16027,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16049,19 +16053,19 @@
         <v>95</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="M115" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>600</v>
-      </c>
       <c r="O115" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
@@ -16110,7 +16114,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16128,27 +16132,27 @@
         <v>83</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AM115" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP115" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP115" t="s" s="2">
-        <v>409</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16174,16 +16178,16 @@
         <v>191</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="N116" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="M116" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>605</v>
-      </c>
       <c r="O116" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -16208,14 +16212,14 @@
         <v>83</v>
       </c>
       <c r="X116" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z116" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="Y116" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="AA116" t="s" s="2">
         <v>83</v>
       </c>
@@ -16232,7 +16236,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16241,7 +16245,7 @@
         <v>94</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>106</v>
@@ -16256,7 +16260,7 @@
         <v>137</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>83</v>
@@ -16267,14 +16271,14 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -16296,16 +16300,16 @@
         <v>191</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="N117" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="M117" t="s" s="2">
+      <c r="O117" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -16330,13 +16334,13 @@
         <v>83</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>83</v>
@@ -16354,7 +16358,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -16372,27 +16376,27 @@
         <v>83</v>
       </c>
       <c r="AL117" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN117" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AM117" t="s" s="2">
+      <c r="AO117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP117" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP117" t="s" s="2">
-        <v>429</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16418,16 +16422,16 @@
         <v>84</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="N118" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="O118" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -16476,7 +16480,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16497,10 +16501,10 @@
         <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>83</v>
